--- a/data/trans_orig/IP74A2_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP74A2_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto según si ha resuelto el alquiler en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Adultos según si tienen resuelto el retraso en los pagos del alquiler en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>410</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2915</t>
+          <t>2879</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5026</t>
+          <t>5056</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>87,63%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>444</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2911</t>
+          <t>2913</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>713</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4494</t>
+          <t>4475</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>77,56%</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>1167</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1363</t>
+          <t>1388</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5193</t>
+          <t>5158</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3377</t>
+          <t>3425</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>86,94%</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2708</t>
+          <t>2445</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>70,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>609</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4404</t>
+          <t>4379</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>75,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1108</t>
+          <t>1204</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5843</t>
+          <t>5795</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>62,85%</t>
         </is>
       </c>
     </row>
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>200</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4277</t>
+          <t>4774</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>766</t>
+          <t>728</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>79,28%</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>453</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4570</t>
+          <t>4588</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5901</t>
+          <t>5939</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>89,09%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3214</t>
+          <t>2929</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7448</t>
+          <t>7499</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7521</t>
+          <t>7580</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14736</t>
+          <t>15077</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12757</t>
+          <t>12144</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21418</t>
+          <t>21346</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,05%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6236</t>
+          <t>6521</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3517</t>
+          <t>3176</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10732</t>
+          <t>10673</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>6357</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>14946</t>
+          <t>15559</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>56,16%</t>
         </is>
       </c>
     </row>
